--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK7"/>
+  <dimension ref="A1:AK22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45897.52083333334</v>
+        <v>45897.5</v>
       </c>
     </row>
     <row r="7">
@@ -1273,127 +1273,2062 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Oued Akbou</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>MC Oran</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="3" t="n">
+        <v>45897.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>MB Rouisset</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>El Bayadh</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="3" t="n">
+        <v>45897.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ES Sétif</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>JS Saoura</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="3" t="n">
+        <v>45897.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ES Mostaganem</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CS Constantine</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="3" t="n">
+        <v>45897.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>USM Alger</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>MC Alger</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="3" t="n">
+        <v>45897.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>CR Belouizdad</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Paradou AC</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="3" t="n">
+        <v>45897.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ASO Chlef</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>USM Khenchela</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3" t="n">
+        <v>45897.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Qatar Stars League</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Al Rayyan</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Al Duhail</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="n">
+        <v>45897.52083333334</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Dhamk</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Al Hazm</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3" t="n">
+        <v>45897.54513888889</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Qatar Stars League</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Al Sadd</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Al Gharafa</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="3" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="3" t="n">
         <v>45897.60416666666</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Neom SC</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="3" t="n">
+        <v>45897.625</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Al Ittifaq</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Al Kholood</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="3" t="n">
+        <v>45897.625</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Faroe Islands Faroe Islands Premier League</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>EB - Streymur</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NSÍ</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="3" t="n">
+        <v>45897.79166666666</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Belarus Vysheyshaya Liga</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Smorgon</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>MKK-Dnepr</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3" t="n">
+        <v>45897.79166666666</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="3" t="n">
+        <v>45897.83333333334</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3" t="n">
+        <v>45897.89930555555</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G20" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G20" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G20" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G20" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G20" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G20" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G20" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G20" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G20" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G20" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G20" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G20" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK22"/>
+  <dimension ref="A1:AK24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45897.83333333334</v>
+        <v>45897.79166666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,126 +3208,384 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Faroe Islands Faroe Islands Premier League</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>EB - Streymur</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NSÍ</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3" t="n">
+        <v>45897.79166666666</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="3" t="n">
+        <v>45897.83333333334</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>21:35</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="3" t="n">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3" t="n">
         <v>45897.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G22" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G22" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK24"/>
+  <dimension ref="A1:AK26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,7 +628,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45897.38541666666</v>
+        <v>45897.25</v>
       </c>
     </row>
     <row r="3">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45897.41666666666</v>
+        <v>45897.38541666666</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45897.5</v>
+        <v>45897.41666666666</v>
       </c>
     </row>
     <row r="7">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45897.52083333334</v>
+        <v>45897.5</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45897.54513888889</v>
+        <v>45897.52083333334</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45897.60416666666</v>
+        <v>45897.52083333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45897.625</v>
+        <v>45897.54513888889</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45897.625</v>
+        <v>45897.60416666666</v>
       </c>
     </row>
     <row r="19">
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45897.79166666666</v>
+        <v>45897.625</v>
       </c>
     </row>
     <row r="20">
@@ -2950,27 +2950,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45897.79166666666</v>
+        <v>45897.625</v>
       </c>
     </row>
     <row r="21">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45897.83333333334</v>
+        <v>45897.79166666666</v>
       </c>
     </row>
     <row r="24">
@@ -3466,126 +3466,384 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Belarus Vysheyshaya Liga</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Smorgon</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>MKK-Dnepr</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3" t="n">
+        <v>45897.79166666666</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3" t="n">
+        <v>45897.83333333334</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>21:35</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="L26" t="n">
         <v>2.34</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M26" t="n">
         <v>2.64</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N26" t="n">
         <v>3.18</v>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
         <v>2.15</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="Z26" t="n">
         <v>1.62</v>
       </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="3" t="n">
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="3" t="n">
         <v>45897.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK26"/>
+  <dimension ref="A1:AK22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45897.5</v>
+        <v>45897.45833333334</v>
       </c>
     </row>
     <row r="8">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45897.5</v>
+        <v>45897.52083333334</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45897.5</v>
+        <v>45897.52083333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45897.5</v>
+        <v>45897.54166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45897.5</v>
+        <v>45897.54166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45897.52083333334</v>
+        <v>45897.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45897.52083333334</v>
+        <v>45897.54166666666</v>
       </c>
     </row>
     <row r="17">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45897.79166666666</v>
+        <v>45897.83333333334</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3328,522 +3328,6 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45897.79166666666</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>45897</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Atlético GO</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" s="3" t="n">
-        <v>45897.79166666666</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>45897</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>EB - Streymur</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>NSÍ</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="3" t="n">
-        <v>45897.79166666666</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>45897</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>La Serena</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" s="3" t="n">
-        <v>45897.83333333334</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>45897</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Remo</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="M26" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="3" t="n">
         <v>45897.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
       <c r="M22" t="n">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45897.45833333334</v>
+        <v>45897.5</v>
       </c>
     </row>
     <row r="8">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45897.52083333334</v>
+        <v>45897.5</v>
       </c>
     </row>
     <row r="12">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45897.54166666666</v>
+        <v>45897.52083333334</v>
       </c>
     </row>
     <row r="14">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G20" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK22"/>
+  <dimension ref="A1:AK25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45897.54166666666</v>
+        <v>45897.52083333334</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45897.54166666666</v>
+        <v>45897.52083333334</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45897.54166666666</v>
+        <v>45897.52083333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45897.54513888889</v>
+        <v>45897.54166666666</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45897.60416666666</v>
+        <v>45897.54166666666</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45897.625</v>
+        <v>45897.54166666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45897.625</v>
+        <v>45897.54513888889</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45897.83333333334</v>
+        <v>45897.60416666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,126 +3208,513 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Neom SC</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3" t="n">
+        <v>45897.625</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Al Ittifaq</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Al Kholood</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="3" t="n">
+        <v>45897.625</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3" t="n">
+        <v>45897.83333333334</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>21:35</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L22" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="L25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O25" t="n">
         <v>3</v>
       </c>
-      <c r="N22" t="n">
-        <v>3</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="P25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S25" t="n">
         <v>2.5</v>
       </c>
-      <c r="T22" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U22" t="n">
+      <c r="T25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U25" t="n">
         <v>1.3</v>
       </c>
-      <c r="V22" t="n">
+      <c r="V25" t="n">
         <v>1.08</v>
       </c>
-      <c r="W22" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y22" t="n">
+      <c r="W25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y25" t="n">
         <v>2.33</v>
       </c>
-      <c r="Z22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA22" t="n">
+      <c r="Z25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA25" t="n">
         <v>4.15</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AB25" t="n">
         <v>1.18</v>
       </c>
-      <c r="AC22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
+      <c r="AC25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
         <v>1.36</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AH25" t="n">
         <v>1.53</v>
       </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="3" t="n">
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3" t="n">
         <v>45897.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK25"/>
+  <dimension ref="A1:AK16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45897.38541666666</v>
+        <v>45897.41666666666</v>
       </c>
     </row>
     <row r="5">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45897.38541666666</v>
+        <v>45897.5</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45897.41666666666</v>
+        <v>45897.5</v>
       </c>
     </row>
     <row r="7">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45897.5</v>
+        <v>45897.52083333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45897.5</v>
+        <v>45897.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45897.52083333334</v>
+        <v>45897.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45897.52083333334</v>
+        <v>45897.54166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45897.52083333334</v>
+        <v>45897.60416666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,27 +2305,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45897.52083333334</v>
+        <v>45897.83333333334</v>
       </c>
     </row>
     <row r="16">
@@ -2434,27 +2434,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,1167 +2554,6 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45897.52083333334</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>45897</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ES Sétif</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>JS Saoura</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" s="3" t="n">
-        <v>45897.54166666666</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>45897</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Oued Akbou</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>MC Oran</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="3" t="n">
-        <v>45897.54166666666</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>45897</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>CR Belouizdad</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Paradou AC</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" s="3" t="n">
-        <v>45897.54166666666</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>45897</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Saudi Arabia Professional League</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Dhamk</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Al Hazm</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" s="3" t="n">
-        <v>45897.54513888889</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>45897</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Qatar Stars League</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Al Sadd</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Al Gharafa</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" s="3" t="n">
-        <v>45897.60416666666</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>45897</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Saudi Arabia Professional League</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Al Ittifaq</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Al Kholood</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="3" t="n">
-        <v>45897.625</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>45897</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Saudi Arabia Professional League</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Al Ahli</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Neom SC</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" s="3" t="n">
-        <v>45897.625</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>45897</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>La Serena</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N24" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="3" t="n">
-        <v>45897.83333333334</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>45897</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Remo</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" s="3" t="n">
         <v>45897.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK16"/>
+  <dimension ref="A1:AK25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45897.41666666666</v>
+        <v>45897.38541666666</v>
       </c>
     </row>
     <row r="5">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45897.5</v>
+        <v>45897.38541666666</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45897.5</v>
+        <v>45897.41666666666</v>
       </c>
     </row>
     <row r="7">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45897.52083333334</v>
+        <v>45897.5</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45897.54166666666</v>
+        <v>45897.5</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45897.54166666666</v>
+        <v>45897.52083333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45897.54166666666</v>
+        <v>45897.52083333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45897.60416666666</v>
+        <v>45897.52083333334</v>
       </c>
     </row>
     <row r="15">
@@ -2305,27 +2305,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45897.83333333334</v>
+        <v>45897.52083333334</v>
       </c>
     </row>
     <row r="16">
@@ -2434,126 +2434,1287 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Qatar Stars League</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Al Rayyan</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Al Duhail</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="3" t="n">
+        <v>45897.52083333334</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Oued Akbou</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>MC Oran</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="3" t="n">
+        <v>45897.54166666666</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>CR Belouizdad</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Paradou AC</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="3" t="n">
+        <v>45897.54166666666</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ES Sétif</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>JS Saoura</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="3" t="n">
+        <v>45897.54166666666</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Dhamk</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Al Hazm</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3" t="n">
+        <v>45897.54513888889</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Qatar Stars League</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Al Sadd</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Al Gharafa</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="3" t="n">
+        <v>45897.60416666666</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Al Ittifaq</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Al Kholood</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3" t="n">
+        <v>45897.625</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Neom SC</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="3" t="n">
+        <v>45897.625</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3" t="n">
+        <v>45897.83333333334</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>21:35</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L16" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="M16" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="O16" t="n">
+      <c r="L25" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="O25" t="n">
         <v>3</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P25" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q25" t="n">
         <v>3.8</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R25" t="n">
         <v>1.49</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S25" t="n">
         <v>2.5</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T25" t="n">
         <v>3.3</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U25" t="n">
         <v>1.3</v>
       </c>
-      <c r="V16" t="n">
+      <c r="V25" t="n">
         <v>1.08</v>
       </c>
-      <c r="W16" t="n">
+      <c r="W25" t="n">
         <v>1.4</v>
       </c>
-      <c r="X16" t="n">
+      <c r="X25" t="n">
         <v>2.75</v>
       </c>
-      <c r="Y16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AA16" t="n">
+      <c r="Y25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA25" t="n">
         <v>4.15</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AB25" t="n">
         <v>1.18</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AC25" t="n">
         <v>1.91</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AD25" t="n">
         <v>1.77</v>
       </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
         <v>1.36</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AH25" t="n">
         <v>1.47</v>
       </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" s="3" t="n">
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3" t="n">
         <v>45897.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK25"/>
+  <dimension ref="A1:AK24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45897.5</v>
+        <v>45897.52083333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45897.5</v>
+        <v>45897.52083333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45897.5</v>
+        <v>45897.52083333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45897.5</v>
+        <v>45897.52083333334</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45897.52083333334</v>
+        <v>45897.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45897.52083333334</v>
+        <v>45897.54166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45897.52083333334</v>
+        <v>45897.54166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45897.52083333334</v>
+        <v>45897.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45897.52083333334</v>
+        <v>45897.54166666666</v>
       </c>
     </row>
     <row r="17">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45897.54166666666</v>
+        <v>45897.54513888889</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45897.54513888889</v>
+        <v>45897.60416666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45897.60416666666</v>
+        <v>45897.625</v>
       </c>
     </row>
     <row r="22">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45897.625</v>
+        <v>45897.83333333334</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,58 +3507,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.7</v>
+        <v>2.34</v>
       </c>
       <c r="M24" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T24" t="n">
         <v>3.3</v>
       </c>
-      <c r="N24" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.04</v>
-      </c>
       <c r="U24" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W24" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X24" t="n">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AD24" t="n">
         <v>1.8</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,135 +3586,6 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45897.83333333334</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>45897</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Remo</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" s="3" t="n">
         <v>45897.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3519,10 +3519,10 @@
         <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
         <v>1.49</v>
@@ -3537,13 +3537,13 @@
         <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W24" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="X24" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Y24" t="n">
         <v>2.15</v>
@@ -3555,7 +3555,7 @@
         <v>4.15</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AC24" t="n">
         <v>1.91</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G17" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK24"/>
+  <dimension ref="A1:AK25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="Z3" t="n">
         <v>1.68</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -936,52 +936,52 @@
         <v>4.2</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Y4" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45897.54166666666</v>
+        <v>45897.52083333334</v>
       </c>
     </row>
     <row r="13">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45897.54513888889</v>
+        <v>45897.54166666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45897.60416666666</v>
+        <v>45897.54513888889</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45897.625</v>
+        <v>45897.60416666666</v>
       </c>
     </row>
     <row r="22">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45897.83333333334</v>
+        <v>45897.625</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,58 +3507,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.34</v>
+        <v>1.7</v>
       </c>
       <c r="M24" t="n">
-        <v>2.64</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.18</v>
+        <v>4.25</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.75</v>
+        <v>5.05</v>
       </c>
       <c r="R24" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="T24" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="X24" t="n">
-        <v>2.6</v>
+        <v>2.93</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AD24" t="n">
         <v>1.8</v>
@@ -3574,18 +3574,147 @@
         </is>
       </c>
       <c r="AG24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3" t="n">
+        <v>45897.83333333334</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
         <v>1.36</v>
       </c>
-      <c r="AH24" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="3" t="n">
+      <c r="AH25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3" t="n">
         <v>45897.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK25"/>
+  <dimension ref="A1:AK24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -936,25 +936,25 @@
         <v>4.2</v>
       </c>
       <c r="O4" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="P4" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.62</v>
+        <v>3.88</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T4" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="U4" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -966,22 +966,22 @@
         <v>3.14</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45897.52083333334</v>
+        <v>45897.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45897.54166666666</v>
+        <v>45897.54513888889</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45897.54513888889</v>
+        <v>45897.60416666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45897.60416666666</v>
+        <v>45897.625</v>
       </c>
     </row>
     <row r="22">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45897.625</v>
+        <v>45897.83333333334</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,58 +3507,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.7</v>
+        <v>2.47</v>
       </c>
       <c r="M24" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T24" t="n">
         <v>3.3</v>
       </c>
-      <c r="N24" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X24" t="n">
         <v>2.65</v>
       </c>
-      <c r="T24" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.93</v>
-      </c>
       <c r="Y24" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AD24" t="n">
         <v>1.8</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,135 +3586,6 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45897.83333333334</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>45897</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Remo</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" s="3" t="n">
         <v>45897.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6</v>
+        <v>3.37</v>
       </c>
       <c r="N5" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>2.24</v>
+        <v>2.75</v>
       </c>
       <c r="P5" t="n">
         <v>2.07</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.7</v>
+        <v>3.88</v>
       </c>
       <c r="R5" t="n">
         <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="T5" t="n">
-        <v>2.99</v>
+        <v>2.76</v>
       </c>
       <c r="U5" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="X5" t="n">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.68</v>
+        <v>3.14</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3510,19 +3510,19 @@
         <v>2.47</v>
       </c>
       <c r="M24" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="N24" t="n">
         <v>3.22</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="R24" t="n">
         <v>1.47</v>
@@ -3537,31 +3537,31 @@
         <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W24" t="n">
         <v>1.43</v>
       </c>
       <c r="X24" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Y24" t="n">
         <v>2.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="M5" t="n">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>2.75</v>
+        <v>2.24</v>
       </c>
       <c r="P5" t="n">
         <v>2.07</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.88</v>
+        <v>5.7</v>
       </c>
       <c r="R5" t="n">
         <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="T5" t="n">
-        <v>2.76</v>
+        <v>2.99</v>
       </c>
       <c r="U5" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="X5" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="Y5" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.14</v>
+        <v>3.68</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="M10" t="n">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="N10" t="n">
-        <v>8.5</v>
+        <v>23</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="M11" t="n">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>23</v>
+        <v>8.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G22" t="n">

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK24"/>
+  <dimension ref="A1:AK26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="M4" t="n">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>2.75</v>
+        <v>2.24</v>
       </c>
       <c r="P4" t="n">
         <v>2.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.88</v>
+        <v>5.7</v>
       </c>
       <c r="R4" t="n">
         <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="T4" t="n">
-        <v>2.76</v>
+        <v>2.99</v>
       </c>
       <c r="U4" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="X4" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="Y4" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.14</v>
+        <v>3.68</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>3.37</v>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>2.24</v>
+        <v>2.75</v>
       </c>
       <c r="P5" t="n">
         <v>2.07</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.7</v>
+        <v>3.88</v>
       </c>
       <c r="R5" t="n">
         <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="T5" t="n">
-        <v>2.99</v>
+        <v>2.76</v>
       </c>
       <c r="U5" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="X5" t="n">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.68</v>
+        <v>3.14</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,65 +1439,65 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.47</v>
+        <v>1.23</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="N8" t="n">
-        <v>7.7</v>
+        <v>10</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Y8" t="n">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.72</v>
+        <v>2.18</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45897.52083333334</v>
+        <v>45897.5</v>
       </c>
     </row>
     <row r="9">
@@ -1710,34 +1710,34 @@
         <v>23</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y10" t="n">
         <v>1.85</v>
@@ -1746,16 +1746,16 @@
         <v>1.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1839,34 +1839,34 @@
         <v>8.5</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y11" t="n">
         <v>2.2</v>
@@ -1875,16 +1875,16 @@
         <v>1.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45897.54166666666</v>
+        <v>45897.52083333334</v>
       </c>
     </row>
     <row r="13">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45897.54513888889</v>
+        <v>45897.54166666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45897.60416666666</v>
+        <v>45897.54513888889</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45897.625</v>
+        <v>45897.60416666666</v>
       </c>
     </row>
     <row r="22">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45897.83333333334</v>
+        <v>45897.625</v>
       </c>
     </row>
     <row r="24">
@@ -3466,126 +3466,384 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ferroviária</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3" t="n">
+        <v>45897.79166666666</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3" t="n">
+        <v>45897.83333333334</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>21:35</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L24" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="M24" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="N24" t="n">
+      <c r="L26" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T26" t="n">
         <v>3.22</v>
       </c>
-      <c r="O24" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U24" t="n">
+      <c r="U26" t="n">
         <v>1.3</v>
       </c>
-      <c r="V24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
+      <c r="V26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
         <v>1.36</v>
       </c>
-      <c r="AH24" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="3" t="n">
+      <c r="AH26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="3" t="n">
         <v>45897.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK26"/>
+  <dimension ref="A1:AK25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>20.59</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>8.69</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="M5" t="n">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>2.75</v>
+        <v>2.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.88</v>
+        <v>5.64</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="T5" t="n">
-        <v>2.76</v>
+        <v>2.99</v>
       </c>
       <c r="U5" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="X5" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45897.41666666666</v>
+        <v>45897.5</v>
       </c>
     </row>
     <row r="7">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1310,65 +1310,65 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45897.5</v>
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,65 +1439,65 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45897.5</v>
+        <v>45897.52083333334</v>
       </c>
     </row>
     <row r="9">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="M10" t="n">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="N10" t="n">
-        <v>23</v>
+        <v>8.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.64</v>
+        <v>2.02</v>
       </c>
       <c r="P10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X10" t="n">
         <v>2.65</v>
       </c>
-      <c r="Q10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.42</v>
-      </c>
       <c r="Y10" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.78</v>
+        <v>4.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.9</v>
+        <v>2.42</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.95</v>
+        <v>2.55</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="N11" t="n">
-        <v>8.5</v>
+        <v>23</v>
       </c>
       <c r="O11" t="n">
-        <v>2.02</v>
+        <v>1.64</v>
       </c>
       <c r="P11" t="n">
-        <v>2.16</v>
+        <v>2.65</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.5</v>
+        <v>10.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="U11" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="X11" t="n">
-        <v>2.65</v>
+        <v>3.42</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.1</v>
+        <v>2.78</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.42</v>
+        <v>2.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.55</v>
+        <v>3.95</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45897.52083333334</v>
+        <v>45897.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45897.54166666666</v>
+        <v>45897.54513888889</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45897.54513888889</v>
+        <v>45897.60416666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45897.60416666666</v>
+        <v>45897.625</v>
       </c>
     </row>
     <row r="22">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45897.625</v>
+        <v>45897.79166666666</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="M24" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.14</v>
+        <v>4.25</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45897.79166666666</v>
+        <v>45897.83333333334</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,58 +3636,58 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.7</v>
+        <v>2.34</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>2.64</v>
       </c>
       <c r="N25" t="n">
-        <v>4.25</v>
+        <v>3.18</v>
       </c>
       <c r="O25" t="n">
-        <v>2.42</v>
+        <v>3.01</v>
       </c>
       <c r="P25" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.05</v>
+        <v>3.87</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="T25" t="n">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="U25" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W25" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="X25" t="n">
-        <v>2.93</v>
+        <v>2.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AD25" t="n">
         <v>1.8</v>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3715,135 +3715,6 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45897.83333333334</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>45897</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Remo</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="M26" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="O26" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="3" t="n">
         <v>45897.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -772,103 +772,103 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="M3" t="n">
         <v>3.4</v>
       </c>
       <c r="N3" t="n">
-        <v>4.32</v>
+        <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="P3" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.8</v>
+        <v>3.31</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>2.58</v>
+        <v>2.95</v>
       </c>
       <c r="T3" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="X3" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.24</v>
+        <v>1.84</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.88</v>
+        <v>3.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31', '66', '72', '76']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['84', '90+1']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.93</v>
+        <v>1.47</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,91 +901,91 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
         <v>3.4</v>
       </c>
       <c r="N4" t="n">
-        <v>3.25</v>
+        <v>4.32</v>
       </c>
       <c r="O4" t="n">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="P4" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.31</v>
+        <v>4.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.95</v>
+        <v>2.58</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="X4" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.84</v>
+        <v>2.24</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.2</v>
+        <v>3.88</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.47</v>
+        <v>1.93</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.05</v>
+        <v>1.11</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="O7" t="n">
-        <v>3.32</v>
+        <v>1.48</v>
       </c>
       <c r="P7" t="n">
-        <v>2.39</v>
+        <v>2.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.5</v>
+        <v>17</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S7" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.17</v>
+        <v>2.48</v>
       </c>
       <c r="U7" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X7" t="n">
-        <v>5.26</v>
+        <v>4.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.62</v>
+        <v>2.23</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.42</v>
+        <v>3.56</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.6</v>
+        <v>1.22</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.34</v>
+        <v>5.5</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,77 +1443,77 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.47</v>
+        <v>3.05</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="N8" t="n">
-        <v>7.7</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.95</v>
+        <v>3.32</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>2.49</v>
+        <v>3.95</v>
       </c>
       <c r="T8" t="n">
-        <v>2.95</v>
+        <v>2.17</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="V8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="X8" t="n">
-        <v>2.64</v>
+        <v>5.26</v>
       </c>
       <c r="Y8" t="n">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.72</v>
+        <v>2.62</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
         <v>1.2</v>
       </c>
-      <c r="AC8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AH8" t="n">
-        <v>2.73</v>
+        <v>1.34</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="O9" t="n">
-        <v>1.47</v>
+        <v>1.85</v>
       </c>
       <c r="P9" t="n">
-        <v>2.69</v>
+        <v>2.03</v>
       </c>
       <c r="Q9" t="n">
-        <v>17</v>
+        <v>8.68</v>
       </c>
       <c r="R9" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>2.94</v>
+        <v>2.32</v>
       </c>
       <c r="T9" t="n">
-        <v>2.48</v>
+        <v>3.14</v>
       </c>
       <c r="U9" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W9" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="X9" t="n">
-        <v>4.3</v>
+        <v>2.85</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.45</v>
+        <v>4.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="AC9" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AH9" t="n">
-        <v>5.5</v>
+        <v>3.15</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O10" t="n">
-        <v>2.42</v>
+        <v>2.29</v>
       </c>
       <c r="P10" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.15</v>
+        <v>6.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="S10" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="T10" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="U10" t="n">
         <v>1.18</v>
       </c>
       <c r="V10" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="W10" t="n">
         <v>1.6</v>
       </c>
       <c r="X10" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="AB10" t="n">
         <v>1.08</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="M11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T11" t="n">
         <v>3.55</v>
       </c>
-      <c r="N11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>6</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.45</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
         <v>1.04</v>
       </c>
       <c r="W11" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="X11" t="n">
         <v>2.43</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AA11" t="n">
         <v>4.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.22</v>
+        <v>1.98</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1959,34 +1959,34 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="O12" t="n">
         <v>2.55</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q12" t="n">
         <v>3.98</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U12" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V12" t="n">
         <v>1.05</v>
@@ -1995,22 +1995,22 @@
         <v>1.22</v>
       </c>
       <c r="X12" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AA12" t="n">
         <v>2.78</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AD12" t="n">
         <v>2.15</v>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2226,25 +2226,25 @@
         <v>3.5</v>
       </c>
       <c r="O14" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="P14" t="n">
         <v>2.19</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="U14" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
         <v>1.04</v>
@@ -2253,25 +2253,25 @@
         <v>1.22</v>
       </c>
       <c r="X14" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="Y14" t="n">
         <v>1.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AA14" t="n">
         <v>2.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AC14" t="n">
         <v>1.63</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="M15" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>4.94</v>
       </c>
       <c r="R15" t="n">
         <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="T15" t="n">
-        <v>2.34</v>
+        <v>2.07</v>
       </c>
       <c r="U15" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="V15" t="n">
         <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X15" t="n">
-        <v>4.98</v>
+        <v>5.24</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.45</v>
+        <v>2.83</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -1168,30 +1168,30 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>15.73</v>
       </c>
       <c r="O6" t="n">
         <v>1.67</v>
@@ -1200,7 +1200,7 @@
         <v>2.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.91</v>
+        <v>8.1</v>
       </c>
       <c r="R6" t="n">
         <v>1.3</v>
@@ -1209,16 +1209,16 @@
         <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="U6" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="V6" t="n">
         <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
         <v>4</v>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19', '21', '54', '57', '61']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['38']</t>
         </is>
       </c>
       <c r="AG6" t="n">
@@ -1297,20 +1297,20 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+2', '90']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,103 +1417,103 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.05</v>
+        <v>1.59</v>
       </c>
       <c r="M8" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>5.27</v>
       </c>
       <c r="O8" t="n">
-        <v>3.32</v>
+        <v>2.31</v>
       </c>
       <c r="P8" t="n">
-        <v>2.39</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.5</v>
+        <v>5.75</v>
       </c>
       <c r="R8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U8" t="n">
         <v>1.25</v>
       </c>
-      <c r="S8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.6</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W8" t="n">
-        <v>1.14</v>
+        <v>1.53</v>
       </c>
       <c r="X8" t="n">
-        <v>5.26</v>
+        <v>2.43</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.43</v>
+        <v>2.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.62</v>
+        <v>1.46</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.65</v>
+        <v>1.16</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.42</v>
+        <v>2.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.6</v>
+        <v>1.49</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
+          <t>['42', '50']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG8" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.34</v>
+        <v>1.98</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,103 +1546,103 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="M9" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>11</v>
+        <v>5.9</v>
       </c>
       <c r="O9" t="n">
-        <v>1.85</v>
+        <v>2.29</v>
       </c>
       <c r="P9" t="n">
-        <v>2.03</v>
+        <v>1.81</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.68</v>
+        <v>6.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="S9" t="n">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="T9" t="n">
-        <v>3.14</v>
+        <v>3.86</v>
       </c>
       <c r="U9" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="V9" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="W9" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>2.85</v>
+        <v>2.18</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.38</v>
+        <v>2.93</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.75</v>
+        <v>5.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.99</v>
+        <v>2.78</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.15</v>
+        <v>2.28</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,16 +1675,16 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1697,81 +1697,81 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.62</v>
+        <v>2.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="N10" t="n">
-        <v>5.9</v>
+        <v>2.1</v>
       </c>
       <c r="O10" t="n">
-        <v>2.29</v>
+        <v>2.92</v>
       </c>
       <c r="P10" t="n">
-        <v>1.81</v>
+        <v>2.43</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.8</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X10" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.65</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AC10" t="n">
-        <v>2.78</v>
+        <v>1.44</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.39</v>
+        <v>2.69</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG10" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.28</v>
+        <v>1.36</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,103 +1804,103 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.59</v>
+        <v>1.36</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>5.27</v>
+        <v>11</v>
       </c>
       <c r="O11" t="n">
-        <v>2.31</v>
+        <v>1.85</v>
       </c>
       <c r="P11" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.75</v>
+        <v>8.68</v>
       </c>
       <c r="R11" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T11" t="n">
-        <v>3.55</v>
+        <v>3.14</v>
       </c>
       <c r="U11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="V11" t="n">
         <v>1.04</v>
       </c>
       <c r="W11" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="X11" t="n">
-        <v>2.43</v>
+        <v>2.85</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.4</v>
+        <v>2.99</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
+          <t>['23', '67', '71']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>1.04</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.98</v>
+        <v>3.15</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="O13" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="P13" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.43</v>
+        <v>4.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
         <v>4.4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="U13" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="V13" t="n">
         <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.97</v>
+        <v>2.55</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,103 +772,103 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['31', '66', '72', '76']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['84', '90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,103 +1030,103 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31', '66', '72', '76']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['84', '90+1']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,77 +1572,77 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.62</v>
+        <v>2.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="N9" t="n">
-        <v>5.9</v>
+        <v>2.1</v>
       </c>
       <c r="O9" t="n">
-        <v>2.29</v>
+        <v>2.92</v>
       </c>
       <c r="P9" t="n">
-        <v>1.81</v>
+        <v>2.43</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.8</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X9" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.65</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AC9" t="n">
-        <v>2.78</v>
+        <v>1.44</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.39</v>
+        <v>2.69</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['23']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.28</v>
+        <v>1.36</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,77 +1701,77 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.7</v>
+        <v>1.62</v>
       </c>
       <c r="M10" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.1</v>
+        <v>5.9</v>
       </c>
       <c r="O10" t="n">
-        <v>2.92</v>
+        <v>2.29</v>
       </c>
       <c r="P10" t="n">
-        <v>2.43</v>
+        <v>1.81</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.5</v>
+        <v>6.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="S10" t="n">
-        <v>3.9</v>
+        <v>2.19</v>
       </c>
       <c r="T10" t="n">
-        <v>2.1</v>
+        <v>3.86</v>
       </c>
       <c r="U10" t="n">
-        <v>1.66</v>
+        <v>1.18</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>1.6</v>
       </c>
       <c r="X10" t="n">
-        <v>5.43</v>
+        <v>2.18</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.5</v>
+        <v>2.93</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.62</v>
+        <v>1.38</v>
       </c>
       <c r="AA10" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH10" t="n">
         <v>2.28</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>['61']</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.36</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+8']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AG12" t="n">
@@ -2071,20 +2071,20 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4', '51']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2191,103 +2191,103 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.92</v>
+        <v>1.35</v>
       </c>
       <c r="M14" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="N14" t="n">
-        <v>3.5</v>
+        <v>7.3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="P14" t="n">
-        <v>2.19</v>
+        <v>2.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.72</v>
+        <v>4.94</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="T14" t="n">
-        <v>2.49</v>
+        <v>2.07</v>
       </c>
       <c r="U14" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="V14" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X14" t="n">
-        <v>3.76</v>
+        <v>5.24</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC14" t="n">
         <v>1.7</v>
       </c>
-      <c r="Z14" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AD14" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG14" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.02</v>
+        <v>2.83</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,103 +2320,103 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.35</v>
+        <v>1.92</v>
       </c>
       <c r="M15" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="N15" t="n">
-        <v>7.3</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.81</v>
+        <v>2.4</v>
       </c>
       <c r="P15" t="n">
-        <v>2.6</v>
+        <v>2.19</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.94</v>
+        <v>3.72</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.07</v>
+        <v>2.49</v>
       </c>
       <c r="U15" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="V15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W15" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X15" t="n">
-        <v>5.24</v>
+        <v>3.76</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.57</v>
+        <v>2.11</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '61']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.83</v>
+        <v>2.02</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,103 +772,103 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31', '66', '72', '76']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['84', '90+1']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,91 +901,91 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['41']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,19 +1030,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1056,77 +1056,77 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
         <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>3.25</v>
+        <v>4.32</v>
       </c>
       <c r="O5" t="n">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="P5" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.31</v>
+        <v>4.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>2.95</v>
+        <v>2.58</v>
       </c>
       <c r="T5" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="X5" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.84</v>
+        <v>2.24</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.2</v>
+        <v>3.88</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['31', '66', '72', '76']</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['84', '90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.47</v>
+        <v>1.93</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,22 +1288,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1314,65 +1314,65 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.11</v>
+        <v>2.7</v>
       </c>
       <c r="M7" t="n">
-        <v>6.5</v>
+        <v>3.85</v>
       </c>
       <c r="N7" t="n">
-        <v>20</v>
+        <v>2.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.48</v>
+        <v>2.92</v>
       </c>
       <c r="P7" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="Q7" t="n">
-        <v>17</v>
+        <v>2.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="T7" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X7" t="n">
-        <v>4.3</v>
+        <v>5.43</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.23</v>
+        <v>2.62</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.56</v>
+        <v>1.44</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.22</v>
+        <v>2.69</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['45+2', '90']</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>5.5</v>
+        <v>1.36</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,77 +1572,77 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.7</v>
+        <v>1.62</v>
       </c>
       <c r="M9" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.1</v>
+        <v>5.9</v>
       </c>
       <c r="O9" t="n">
-        <v>2.92</v>
+        <v>2.29</v>
       </c>
       <c r="P9" t="n">
-        <v>2.43</v>
+        <v>1.81</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>6.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="S9" t="n">
-        <v>3.9</v>
+        <v>2.19</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1</v>
+        <v>3.86</v>
       </c>
       <c r="U9" t="n">
-        <v>1.66</v>
+        <v>1.18</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W9" t="n">
-        <v>1.15</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>5.43</v>
+        <v>2.18</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.5</v>
+        <v>2.93</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.62</v>
+        <v>1.38</v>
       </c>
       <c r="AA9" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH9" t="n">
         <v>2.28</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>['61']</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.36</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,103 +1675,103 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>17</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
         <v>1.18</v>
       </c>
-      <c r="V10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.6</v>
-      </c>
       <c r="X10" t="n">
-        <v>2.18</v>
+        <v>4.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.93</v>
+        <v>1.63</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.38</v>
+        <v>2.23</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.55</v>
+        <v>2.63</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.08</v>
+        <v>1.45</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.78</v>
+        <v>3.56</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['45+2', '90']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['23']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.28</v>
+        <v>5.5</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
         <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,77 +2217,77 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>1.92</v>
       </c>
       <c r="M14" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="N14" t="n">
-        <v>7.3</v>
+        <v>3.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.81</v>
+        <v>2.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.6</v>
+        <v>2.19</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.94</v>
+        <v>3.72</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.07</v>
+        <v>2.49</v>
       </c>
       <c r="U14" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W14" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X14" t="n">
-        <v>5.24</v>
+        <v>3.76</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.57</v>
+        <v>2.11</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['23']</t>
+          <t>['7', '61']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.83</v>
+        <v>2.02</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,77 +2346,77 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.92</v>
+        <v>1.35</v>
       </c>
       <c r="M15" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="N15" t="n">
-        <v>3.5</v>
+        <v>7.3</v>
       </c>
       <c r="O15" t="n">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="P15" t="n">
-        <v>2.19</v>
+        <v>2.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.72</v>
+        <v>4.94</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="T15" t="n">
-        <v>2.49</v>
+        <v>2.07</v>
       </c>
       <c r="U15" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="V15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X15" t="n">
-        <v>3.76</v>
+        <v>5.24</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC15" t="n">
         <v>1.7</v>
       </c>
-      <c r="Z15" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AD15" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['7', '61']</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['36']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.02</v>
+        <v>2.83</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>

--- a/jogos_2025-08-28.xlsx
+++ b/jogos_2025-08-28.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,103 +772,103 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['31', '66', '72', '76']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['84', '90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,103 +901,103 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
+          <t>['41']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,19 +1030,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1056,77 +1056,77 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="M5" t="n">
         <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>4.32</v>
+        <v>3.25</v>
       </c>
       <c r="O5" t="n">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.8</v>
+        <v>3.31</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>2.58</v>
+        <v>2.95</v>
       </c>
       <c r="T5" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="X5" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.24</v>
+        <v>1.84</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.88</v>
+        <v>3.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['41']</t>
+          <t>['31', '66', '72', '76']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['84', '90+1']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.93</v>
+        <v>1.47</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,77 +1314,77 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.7</v>
+        <v>1.62</v>
       </c>
       <c r="M7" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.1</v>
+        <v>5.9</v>
       </c>
       <c r="O7" t="n">
-        <v>2.92</v>
+        <v>2.29</v>
       </c>
       <c r="P7" t="n">
-        <v>2.43</v>
+        <v>1.81</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.5</v>
+        <v>6.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="S7" t="n">
-        <v>3.9</v>
+        <v>2.19</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1</v>
+        <v>3.86</v>
       </c>
       <c r="U7" t="n">
-        <v>1.66</v>
+        <v>1.18</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W7" t="n">
-        <v>1.15</v>
+        <v>1.6</v>
       </c>
       <c r="X7" t="n">
-        <v>5.43</v>
+        <v>2.18</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.5</v>
+        <v>2.93</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.62</v>
+        <v>1.38</v>
       </c>
       <c r="AA7" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH7" t="n">
         <v>2.28</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>['61']</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.36</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,22 +1417,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1443,65 +1443,65 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.59</v>
+        <v>2.7</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N8" t="n">
-        <v>5.27</v>
+        <v>2.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2.31</v>
+        <v>2.92</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>2.43</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.75</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X8" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA8" t="n">
         <v>2.28</v>
       </c>
-      <c r="T8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AB8" t="n">
-        <v>1.16</v>
+        <v>1.65</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.49</v>
+        <v>2.69</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['42', '50']</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.98</v>
+        <v>1.36</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,77 +1572,77 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="O9" t="n">
-        <v>2.29</v>
+        <v>1.85</v>
       </c>
       <c r="P9" t="n">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.8</v>
+        <v>8.68</v>
       </c>
       <c r="R9" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="T9" t="n">
-        <v>3.86</v>
+        <v>3.14</v>
       </c>
       <c r="U9" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="V9" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="X9" t="n">
-        <v>2.18</v>
+        <v>2.85</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.93</v>
+        <v>2.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.55</v>
+        <v>4.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.78</v>
+        <v>2.99</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['23', '67', '71']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['23']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.28</v>
+        <v>1.04</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.28</v>
+        <v>3.15</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1804,16 +1804,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1830,65 +1830,65 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="M11" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>11</v>
+        <v>5.27</v>
       </c>
       <c r="O11" t="n">
-        <v>1.85</v>
+        <v>2.31</v>
       </c>
       <c r="P11" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.68</v>
+        <v>5.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="S11" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="T11" t="n">
-        <v>3.14</v>
+        <v>3.55</v>
       </c>
       <c r="U11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
         <v>1.04</v>
       </c>
       <c r="W11" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="X11" t="n">
-        <v>2.85</v>
+        <v>2.43</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.99</v>
+        <v>2.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['23', '67', '71']</t>
+          <t>['42', '50']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.15</v>
+        <v>1.98</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="N17" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="O17" t="n">
         <v>3.3</v>
@@ -2622,43 +2622,43 @@
         <v>3.46</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="T17" t="n">
         <v>3.34</v>
       </c>
       <c r="U17" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="V17" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="W17" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="X17" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.49</v>
+        <v>2.97</v>
       </c>
       <c r="Z17" t="n">
         <v>1.54</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.77</v>
+        <v>6.17</v>
       </c>
       <c r="AB17" t="n">
         <v>1.14</v>
       </c>
       <c r="AC17" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AH17" t="n">
         <v>1.44</v>
